--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N54_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N54_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.24811105402124</v>
+        <v>5.077818046278452</v>
       </c>
       <c r="D2" t="n">
-        <v>24.86088863575814</v>
+        <v>4.039894403310699</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3372385158578</v>
+        <v>1.679801258826893</v>
       </c>
       <c r="F2" t="n">
-        <v>10.04744501477293</v>
+        <v>1.632709814900601</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.02167448773609</v>
+        <v>6.666022104257114</v>
       </c>
       <c r="D3" t="n">
-        <v>40.11545836706842</v>
+        <v>6.518761984648618</v>
       </c>
       <c r="E3" t="n">
-        <v>10.3372385158578</v>
+        <v>1.679801258826893</v>
       </c>
       <c r="F3" t="n">
-        <v>10.04744501477293</v>
+        <v>1.632709814900601</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.85609800399157</v>
+        <v>4.36411592564863</v>
       </c>
       <c r="D4" t="n">
-        <v>19.4483760229889</v>
+        <v>3.160361103735696</v>
       </c>
       <c r="E4" t="n">
-        <v>10.3372385158578</v>
+        <v>1.679801258826893</v>
       </c>
       <c r="F4" t="n">
-        <v>10.04744501477293</v>
+        <v>1.632709814900601</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.31274268709586</v>
+        <v>2.000820686653077</v>
       </c>
       <c r="D5" t="n">
-        <v>12.90582204951981</v>
+        <v>2.097196083046969</v>
       </c>
       <c r="E5" t="n">
-        <v>10.3372385158578</v>
+        <v>1.679801258826893</v>
       </c>
       <c r="F5" t="n">
-        <v>10.04744501477293</v>
+        <v>1.632709814900601</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
